--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-004_月次勤怠取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-004_月次勤怠取得_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="10477500"/>
+    <ext cx="8572500" cy="10677525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-004 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-004 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="79" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1879,7 +1879,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：型変換エラーの扱いを ONL-001 の共通基盤追加改修（handleTypeMismatch）参照に更新、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：型変換エラーの扱いを ONL-001 の共通基盤追加改修（handleTypeMismatch）参照に更新、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、トークン有効期限を2時間に更新（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3277,7 +3278,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Controller: Long.valueOf(jwt.getSubject())。他人の userId は受け取らない</t>
+          <t>Controller: Long.valueOf(auth.getName())。他人の userId は受け取らない</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3543,7 +3544,7 @@
         <is>
           <t>public MonthlyAttendanceResponse getMonthly(
     @RequestParam(name = "month", required = false) String month,
-    @AuthenticationPrincipal Jwt jwt)</t>
+    Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -3627,17 +3628,17 @@
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub = users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -3684,7 +3685,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return attendanceService.getMonthly(userId, month);</t>
         </is>
       </c>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-004_月次勤怠取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-004_月次勤怠取得_オンライン詳細設計書.xlsx
@@ -273,7 +273,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="3895725"/>
+    <ext cx="10953750" cy="5705475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -303,7 +303,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="8277225"/>
+    <ext cx="10953750" cy="10144125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -330,10 +330,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="10677525"/>
+    <ext cx="8572500" cy="11877675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-004 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-004 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -992,7 +992,7 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="10" t="n"/>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="49" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>本人のデータのみ</t>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>検索条件の user_id は JWT の sub だけから決め、クエリ・パスで他人の userId を指定する手段を設けない。上長・管理者であっても本 API では自分の勤怠しか返らない（部下の勤怠は ONL-018/020 の別 API）。ロール制限はなく全員が自分の勤怠を参照できる。</t>
+          <t>検索条件の user_id は JWT の sub だけから決め、クエリ・パスで他人の userId を指定する手段を設けない。上長・管理者であっても本 API では自分の勤怠しか返らない（部下の勤怠は ONL-018/020 の別 API）。ロール制限はなく全員が自分の勤怠を参照できる。区間（breaks）も、本人の打刻行に属するものだけを attendance_record_id で取得する。</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -1052,7 +1052,7 @@
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="10" t="n"/>
     </row>
-    <row r="17" ht="34" customHeight="1">
+    <row r="17" ht="49" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>未対応・制約</t>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>暦日の空白埋め・休日／休暇種別の表示は行わない。不正な month は Service の検証で E-002 を返す。他の API の型変換エラー（パス変数・クエリ型不一致）は ONL-001 の handleTypeMismatch が E-002 / 400 にする。INACTIVE ユーザーのトークンは有効期限内なら使える（ONL-001 と同じ）。</t>
+          <t>暦日の空白埋め・休日／休暇種別の表示は行わない。不正な month は Service の検証で E-002 を返す。他の API の型変換エラー（パス変数・クエリ型不一致）は ONL-001 の handleTypeMismatch が E-002 / 400 にする。INACTIVE ユーザー・パスワード変更後の旧トークンは ActiveUserFilter により 401 / E-001 になる。</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>①month は String で受け Service で検証（E-002 のメッセージ 3 種）。②応答は打刻のある日のみ。③合計は null を 0 とみなす。④最大 31 件のためページングなし（画面共通仕様の「1ページ20件」は適用しない）。</t>
+          <t>①month は String で受け Service で検証（E-002 のメッセージ 3 種）。②応答は打刻のある日のみ。③合計は null を 0 とみなす。④最大 31 件のためページングなし（画面共通仕様の「1ページ20件」は適用しない）。 ⑤区間は月分を IN 句 1 回で取得（N+1 回避）。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -1105,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E30"/>
+  <dimension ref="A2:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="49" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>records 3件（勤務日昇順）、totalWork = 985、totalOvertime = 30</t>
+          <t>records 3件（勤務日昇順）、totalWork = 985、totalOvertime = 30。各 item に breaks が付く</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1477,283 +1477,295 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>10/1 に BREAK（12:00-12:30）、10/3 に継続中の AWAY（end=NULL）の区間がある</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>10/1 の breaks = [BREAK 12:00:00+09:00〜12:30:00+09:00]、10/3 の breaks = [AWAY 開始のみ・endAt=null]、10/2 の breaks = []</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>区間のない日は null ではなく空リスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>同一日に区間が 2 件（AWAY 10:00-10:30、BREAK 12:00-13:00）</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>breaks は開始時刻の昇順で 2 件</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Repository の ORDER BY start_at に依存</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>打刻行が 0 件</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>区間の問合せ（findByAttendanceRecordIdIn…）は呼ばれない。records = []</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>recs.isEmpty() の分岐</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="49" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>打刻行が複数あり、区間が一部の日にだけある</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>findByAttendanceRecordIdIn… は 1 回だけ呼ばれ、各日に正しく振り分けられる（N+1 にならない）</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>verify(times(1))</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>9.2 AttendanceRecordRepository（@DataJpaTest + PostgreSQL / Testcontainers）</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>9/30・10/1・10/31・11/1 の行を登録して 10月を検索</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>10/1 と 10/31 のみ、昇順</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>範囲境界</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>他ユーザーの10月の行も存在</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>自分の行だけが返る</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>user_id 条件</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>登録順をばらばら（10/3, 10/1, 10/2）にする</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>work_date 昇順で返る</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>ORDER BY</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="26" ht="49" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceBreakRepository：他ユーザー・他月の打刻行に属する区間も存在する状態で、10月の打刻行 id 一覧で検索</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>指定した打刻行の区間だけが start_at 昇順で返る</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>@DataJpaTest（PostgreSQL / Testcontainers）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>9.3 AttendanceController（MockMvc / API テスト）</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>有効 JWT・month=2026-10</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>200、records[]（workDate=yyyy-MM-dd、clockIn=+09:00 付き ISO）、合計2項目</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>null 項目は null で出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>month パラメータなし</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>400 E-002「対象月は必須入力です。」、fieldErrors は []</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>month=2026-99</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>400 E-002「対象月は yyyy-MM 形式で入力してください。」</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Authorization ヘッダなし</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>role = EMPLOYEE / MANAGER / ADMIN の各トークン</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>いずれも 200（自分の勤怠のみ）</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>全ロール可</t>
         </is>
       </c>
     </row>
@@ -1770,25 +1782,175 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
+          <t>有効 JWT・month=2026-10</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>200、records[]（workDate=yyyy-MM-dd、clockIn=+09:00 付き ISO）、合計2項目</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>null 項目は null で出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>month パラメータなし</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>400 E-002「対象月は必須入力です。」、fieldErrors は []</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>month=2026-99</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>400 E-002「対象月は yyyy-MM 形式で入力してください。」</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Authorization ヘッダなし</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>role = EMPLOYEE / MANAGER / ADMIN の各トークン</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>いずれも 200（自分の勤怠のみ）</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>全ロール可</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
           <t>クエリに userId=999 を付与</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>無視され、JWT の sub のユーザーの勤怠が返る</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>他人の勤怠は取得不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="49" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>区間のある日を含む月で GET</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>200、records[].breaks[].startAt / endAt が +09:00 付き。継続中は endAt = null</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>JSON 構造の確認</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1801,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1884,6 +2046,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="94" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席対応：応答の records[] に breaks[]（kind / startAt / endAt）を追加。月内の区間を attendance_breaks から IN 句で 1 回取得する手順（⑦）、AttendanceItem の 6 引数化、BreakItem の追加、使用テーブル（attendance_breaks: R）・マッピング・SQL・テスト観点を更新。401 のメッセージを実装に合わせて「認証が必要です。再度ログインしてください。」に修正</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1897,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F34"/>
+  <dimension ref="A2:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1984,7 +2169,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>目的</t>
@@ -1992,7 +2177,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ログインユーザー本人の、指定した月の打刻記録を勤務日の昇順で返し、月の勤務時間・残業時間の合計（分）も併せて返す。</t>
+          <t>ログインユーザー本人の、指定した月の打刻記録を勤務日の昇順で返し、月の勤務時間・残業時間の合計（分）も併せて返す。各日には、その日の休憩・日中離席の区間（breaks。ONL-024/025 で打刻したもの）を開始順に含める。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -2040,7 +2225,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>データ更新なし（attendance_records は参照のみ）。レスポンスに records[] と合計を含む。</t>
+          <t>データ更新なし（attendance_records / attendance_breaks は参照のみ）。レスポンスに records[]（各日の breaks[] を含む）と合計を含む。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -2056,7 +2241,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>attendance_records: R</t>
+          <t>attendance_records: R / attendance_breaks: R</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2064,7 +2249,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>トランザクション</t>
@@ -2072,7 +2257,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>読み取り専用（AttendanceService#getMonthly に @Transactional(readOnly = true)）</t>
+          <t>読み取り専用（AttendanceService#getMonthly に @Transactional(readOnly = true)）。打刻行と区間の 2 回の SELECT を同一の読取りトランザクションで行う</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -2225,7 +2410,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>attendance_records テーブル・インデックス idx_att_user_date</t>
+          <t>attendance_records テーブル・インデックス idx_att_user_date／attendance_breaks（V4）・idx_attendance_breaks_record</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -2245,7 +2430,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>対象月（必須・未来月不可＝E-002）・一覧・月合計</t>
+          <t>対象月（必須・未来月不可＝E-002）・一覧・月合計・「休憩・離席」列（breaks の表示）</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -2272,170 +2457,146 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席開始</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>BreakItem / AttendanceBreakRepository / AttendanceBreak の定義元</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>ONL-025</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席終了</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>区間の終了（endAt の設定）</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>controller</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>AttendanceController</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>打刻・月次勤怠の API 入口（本処理で getMonthly を追加）</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>controller/AttendanceController.java</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="49" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="30" ht="49" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>AttendanceService</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>月次勤怠の取得・集計（本処理で getMonthly / parseMonth を追加）</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>service/AttendanceService.java</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-002 で定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="49" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>repository</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>AttendanceRecordRepository</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>月範囲検索 findByUserIdAndWorkDateBetweenOrderByWorkDateAsc を追加</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>repository/AttendanceRecordRepository.java</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-002 で定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>AttendanceRecord</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>attendance_records テーブルのマッピング</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>entity/AttendanceRecord.java</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2447,138 +2608,299 @@
     <row r="31" ht="49" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>dto</t>
+          <t>repository</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>MonthlyAttendanceResponse</t>
+          <t>AttendanceRecordRepository</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>DTO(record)</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>正常応答（records[], totalWorkMinutes, totalOvertimeMinutes）</t>
+          <t>月範囲検索 findByUserIdAndWorkDateBetweenOrderByWorkDateAsc を追加</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>dto/MonthlyAttendanceResponse.java</t>
+          <t>repository/AttendanceRecordRepository.java</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
+          <t>既存（ONL-002 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="79" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>dto</t>
+          <t>repository</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>AttendanceItem</t>
+          <t>AttendanceBreakRepository</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>DTO(record)</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>日別の明細（1日1件）</t>
+          <t>月内の全打刻行の区間を 1 回で取得する findByAttendanceRecordIdInOrderByStartAtAsc を使用（ONL-024 で定義したリポジトリに本処理で追加）</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>dto/AttendanceItem.java</t>
+          <t>repository/AttendanceBreakRepository.java</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>既存（ONL-024 で定義）＋メソッド追加</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceRecord</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>attendance_records テーブルのマッピング</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>entity/AttendanceRecord.java</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-002 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="49" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceBreak</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>attendance_breaks テーブルのマッピング。本処理は読取りのみ</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>entity/AttendanceBreak.java</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-024 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="49" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>MonthlyAttendanceResponse</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>正常応答（records[], totalWorkMinutes, totalOvertimeMinutes）</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>dto/MonthlyAttendanceResponse.java</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceItem</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>日別の明細（1日1件。休憩・離席の区間 breaks[] を含む）</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>dto/AttendanceItem.java</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>新規（ONL-004）。breaks は休憩・離席対応で追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>ClockConfig / AppTime</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Configuration / Utility</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Clock Bean（当月判定に使用）／toIso()</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>config/ClockConfig.java, config/AppTime.java</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>BusinessException / GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Exception / ControllerAdvice</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>業務エラーの保持と共通エラー応答への変換</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>exception/*.java</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 で定義）</t>
         </is>
       </c>
     </row>
+    <row r="39" ht="49" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>BreakItem</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>区間 1 件（kind, startAt, endAt）。ONL-024/025 の応答と共用</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>dto/BreakItem.java</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-024 で定義）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="24">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C18:F18"/>
@@ -2587,15 +2909,16 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C25:F25"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2686,7 +3009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F26"/>
+  <dimension ref="A2:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2953,7 +3276,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>休憩控除後。退勤前は null</t>
+          <t>休憩・離席の控除後。退勤前は null</t>
         </is>
       </c>
       <c r="E15" s="9" t="n"/>
@@ -2986,22 +3309,22 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>totalWorkMinutes</t>
+          <t>records[].breaks</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>月合計勤務時間（分）</t>
+          <t>休憩・離席の区間</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>List&lt;BreakItem&gt;</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>records の workMinutes の合計（null は加算しない）。0 件なら 0</t>
+          <t>その日の区間を開始時刻の昇順で返す。区間がない日は空配列 []（null にしない）</t>
         </is>
       </c>
       <c r="E17" s="9" t="n"/>
@@ -3010,202 +3333,305 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>totalOvertimeMinutes</t>
+          <t>records[].breaks[].kind</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>月合計残業時間（分）</t>
+          <t>種別</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>records の overtimeMinutes の合計。0 件なら 0</t>
+          <t>BREAK（休憩）／ AWAY（日中離席）</t>
         </is>
       </c>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="10" t="n"/>
     </row>
-    <row r="19" ht="184" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>records[].breaks[].startAt</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>開始時刻</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>ISO 8601（JST・+09:00 付き）</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>records[].breaks[].endAt</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>終了時刻</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>同上。継続中（まだ終了していない）区間は null</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>totalWorkMinutes</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>月合計勤務時間（分）</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>records の workMinutes の合計（null は 0 として加算）。0 件なら 0</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>totalOvertimeMinutes</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>月合計残業時間（分）</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>records の overtimeMinutes の合計。0 件なら 0</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="244" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>レスポンス例</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>{
   "records": [
-    { "workDate": "2026-10-01", "clockIn": "2026-10-01T09:00:00+09:00", "clockOut": "2026-10-01T18:30:00+09:00", "workMinutes": 510, "overtimeMinutes": 30 },
-    { "workDate": "2026-10-02", "clockIn": "2026-10-02T09:05:00+09:00", "clockOut": "2026-10-02T18:00:00+09:00", "workMinutes": 475, "overtimeMinutes": 0 },
-    { "workDate": "2026-10-03", "clockIn": "2026-10-03T09:00:00+09:00", "clockOut": null, "workMinutes": null, "overtimeMinutes": null }
+    { "workDate": "2026-10-01", "clockIn": "2026-10-01T09:00:00+09:00", "clockOut": "2026-10-01T18:30:00+09:00", "workMinutes": 510, "overtimeMinutes": 30,
+      "breaks": [ { "kind": "BREAK", "startAt": "2026-10-01T12:00:00+09:00", "endAt": "2026-10-01T12:30:00+09:00" } ] },
+    { "workDate": "2026-10-02", "clockIn": "2026-10-02T09:05:00+09:00", "clockOut": "2026-10-02T18:00:00+09:00", "workMinutes": 475, "overtimeMinutes": 0,
+      "breaks": [] },
+    { "workDate": "2026-10-03", "clockIn": "2026-10-03T09:00:00+09:00", "clockOut": null, "workMinutes": null, "overtimeMinutes": null,
+      "breaks": [ { "kind": "AWAY", "startAt": "2026-10-03T10:00:00+09:00", "endAt": null } ] }
   ],
   "totalWorkMinutes": 985,
   "totalOvertimeMinutes": 30
 }</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>4.3 レスポンス（エラー）  共通形式 ErrorResponse</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>項目名</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>論理名</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>エラーコード</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>E-xxx（8. エラー一覧）</t>
-        </is>
-      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>メッセージ</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>画面に表示する文言（日本語）</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>fieldErrors</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>項目別エラー</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>[{field, message}]。入力チェックエラー時のみ要素あり、それ以外は空配列</t>
-        </is>
-      </c>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>4.3 レスポンス（エラー）  共通形式 ErrorResponse</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="139" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>エラーコード</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>E-xxx（8. エラー一覧）</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>メッセージ</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>画面に表示する文言（日本語）</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>fieldErrors</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>項目別エラー</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>[{field, message}]。入力チェックエラー時のみ要素あり、それ以外は空配列</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="124" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>エラー例</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>HTTP 400（month 未指定）
 { "code": "E-002", "message": "対象月は必須入力です。", "fieldErrors": [] }
 HTTP 400（未来月）
 { "code": "E-002", "message": "対象月に未来の月は指定できません。", "fieldErrors": [] }
 HTTP 401（トークンなし・期限切れ・不正。AuthenticationEntryPoint が返す JSON。Controller には到達しない）
-{ "code": "E-001", "message": "認証情報が無効、または有効期限が切れています。再度ログインしてください。", "fieldErrors": [] }</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="10" t="n"/>
+{ "code": "E-001", "message": "認証が必要です。再度ログインしてください。", "fieldErrors": [] }</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="24">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D27:F27"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D24:F24"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="D19:F19"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3218,7 +3644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F13"/>
+  <dimension ref="A2:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3398,7 +3824,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>findByUserIdAndWorkDateBetweenOrderByWorkDateAsc(userId, from, to)</t>
+          <t>findByUserIdAndWorkDateBetweenOrderByWorkDateAsc(userId, from, to)。0 件なら ⑦ をスキップ</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -3409,7 +3835,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="79" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>⑦</t>
@@ -3417,12 +3843,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>明細へ変換し合計を算出</t>
+          <t>月内の休憩・離席の区間をまとめて取得</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>AttendanceItem に変換。workMinutes / overtimeMinutes は null を除いて合計</t>
+          <t>AttendanceBreakRepository#findByAttendanceRecordIdInOrderByStartAtAsc(打刻行の id 一覧) を 1 回だけ実行（日ごとの N+1 を避ける）し、attendance_record_id ごとにグループ化して BreakItem に変換。打刻行が 0 件なら問合せしない</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3433,7 +3859,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1">
+    <row r="11" ht="79" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>⑧</t>
@@ -3441,12 +3867,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>レスポンス返却</t>
+          <t>明細へ変換し合計を算出</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>MonthlyAttendanceResponse を HTTP 200 で返す</t>
+          <t>AttendanceItem（workDate, clockIn, clockOut, workMinutes, overtimeMinutes, breaks）に変換。breaks は打刻行の id に対応する区間（なければ空リスト）。workMinutes / overtimeMinutes は null を 0 として合計</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3457,25 +3883,50 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>レスポンス返却</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>MonthlyAttendanceResponse を HTTP 200 で返す</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>5.2 処理フロー図</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="10" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
@@ -3495,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F81"/>
+  <dimension ref="A2:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3778,7 +4229,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>month を検証して対象月の期間を求め、本人の打刻記録を取得して明細と合計に変換する。</t>
+          <t>month を検証して対象月の期間を求め、本人の打刻記録と、その月の休憩・離席の区間をまとめて取得し、明細（区間つき）と合計に変換する。</t>
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
@@ -3894,7 +4345,7 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="184" customHeight="1">
+    <row r="26" ht="229" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -3903,17 +4354,20 @@
       <c r="B26" s="12" t="inlineStr">
         <is>
           <t>YearMonth ym = parseMonth(month);                               // ②③④
-LocalDate from = ym.atDay(1);                                   // ⑤
-LocalDate to   = ym.atEndOfMonth();
-List&lt;AttendanceRecord&gt; rows = attendanceRecordRepository
-    .findByUserIdAndWorkDateBetweenOrderByWorkDateAsc(userId, from, to);   // ⑥
-List&lt;AttendanceItem&gt; items = rows.stream()
-    .map(AttendanceService::toItem).toList();                   // ⑦
-int totalWork = rows.stream().map(AttendanceRecord::getWorkMinutes)
-    .filter(Objects::nonNull).mapToInt(Integer::intValue).sum();
-int totalOver = rows.stream().map(AttendanceRecord::getOvertimeMinutes)
-    .filter(Objects::nonNull).mapToInt(Integer::intValue).sum();
-return new MonthlyAttendanceResponse(items, totalWork, totalOver);     // ⑧</t>
+List&lt;AttendanceRecord&gt; recs = repository
+    .findByUserIdAndWorkDateBetweenOrderByWorkDateAsc(
+        userId, ym.atDay(1), ym.atEndOfMonth());                // ⑤⑥
+// 休憩・離席は月分をまとめて取得する（1日ごとに問い合わせない）
+Map&lt;Long, List&lt;BreakItem&gt;&gt; breaks = recs.isEmpty() ? Map.of()   // ⑦ 0件なら問合せしない
+    : breakRepository.findByAttendanceRecordIdInOrderByStartAtAsc(
+            recs.stream().map(AttendanceRecord::getId).toList())
+        .stream().collect(groupingBy(AttendanceBreak::getAttendanceRecordId,
+                mapping(AttendanceService::toBreakItem, toList())));
+List&lt;AttendanceItem&gt; items = recs.stream()
+    .map(r -&gt; toItem(r, breaks.getOrDefault(r.getId(), List.of()))).toList();   // ⑧
+int work     = items.stream().mapToInt(i -&gt; i.workMinutes() == null ? 0 : i.workMinutes()).sum();
+int overtime = items.stream().mapToInt(i -&gt; i.overtimeMinutes() == null ? 0 : i.overtimeMinutes()).sum();
+return new MonthlyAttendanceResponse(items, work, overtime);    // ⑨</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -3921,7 +4375,7 @@
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>呼出先</t>
@@ -3929,7 +4383,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>parseMonth / AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc / toItem</t>
+          <t>parseMonth / AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc / AttendanceBreakRepository#findByAttendanceRecordIdInOrderByStartAtAsc / toItem / toBreakItem</t>
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
@@ -3937,7 +4391,7 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
-    <row r="28" ht="79" customHeight="1">
+    <row r="28" ht="124" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -3946,8 +4400,9 @@
       <c r="B28" s="7" t="inlineStr">
         <is>
           <t>【本人のみ】検索条件の user_id には引数 userId（JWT の sub）だけを使う。
+【区間の取得】区間は attendance_record_id の IN 句で月分を 1 回の SELECT で取得し（最大 31 日分）、Java 側でグループ化する。取得結果は start_at 昇順なので、各日の breaks も開始順になる。区間のない日は空リスト。
 【空白埋めしない】打刻記録がある日だけ返す。休日・休暇日・未打刻日を含む暦日一覧の生成と、休暇種別の表示は画面側（または将来の別 API）の責務とする（KF-DD-001 の使用テーブルが attendance_records のみのため）。
-【合計】null（退勤前）は 0 として扱う。int の合計は最大でも 31日×1440分で overflow しない。
+【合計】null（退勤前）は 0 として扱う（items から合計。区間の控除は退勤時に work_minutes へ反映済みのため、合計は work_minutes の足し上げのみ）。int の合計は最大でも 31日×1440分で overflow しない。
 【件数】最大31件のためページングなし。</t>
         </is>
       </c>
@@ -4192,7 +4647,7 @@
       <c r="E44" s="9" t="n"/>
       <c r="F44" s="10" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1">
+    <row r="45" ht="34" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -4200,7 +4655,8 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>private static AttendanceItem toItem(AttendanceRecord r)</t>
+          <t>private static AttendanceItem toItem(AttendanceRecord r, List&lt;BreakItem&gt; breaks)
+private static BreakItem toBreakItem(AttendanceBreak b)</t>
         </is>
       </c>
       <c r="C45" s="9" t="n"/>
@@ -4216,7 +4672,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Entity を明細 DTO に変換する。</t>
+          <t>Entity を明細 DTO に変換する（区間は呼出し側で用意した BreakItem のリストを渡す）。</t>
         </is>
       </c>
       <c r="C46" s="9" t="n"/>
@@ -4281,83 +4737,93 @@
       <c r="F49" s="10" t="n"/>
     </row>
     <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>breaks</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>AttendanceItem</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="n"/>
+          <t>List&lt;BreakItem&gt;</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>その日の区間（開始順。なければ空リスト）</t>
+        </is>
+      </c>
       <c r="D50" s="9" t="n"/>
       <c r="E50" s="9" t="n"/>
       <c r="F50" s="10" t="n"/>
     </row>
     <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>例外</t>
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="n"/>
+          <t>AttendanceBreak</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>区間 1 件</t>
+        </is>
+      </c>
       <c r="D51" s="9" t="n"/>
       <c r="E51" s="9" t="n"/>
       <c r="F51" s="10" t="n"/>
     </row>
-    <row r="52" ht="94" customHeight="1">
+    <row r="52" ht="19" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceItem</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="10" t="n"/>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="10" t="n"/>
+    </row>
+    <row r="54" ht="139" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
           <t>処理詳細</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>return new AttendanceItem(
     r.getWorkDate().toString(),            // yyyy-MM-dd
     AppTime.toIso(r.getClockIn()),         // null なら null
     AppTime.toIso(r.getClockOut()),
     r.getWorkMinutes(),                    // Integer（null 可）
-    r.getOvertimeMinutes());</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="10" t="n"/>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>呼出先</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>AppTime#toIso</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
-      <c r="E53" s="9" t="n"/>
-      <c r="F53" s="10" t="n"/>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Entity を画面に直接返さない（KF-DD-002 層間IF）。user_id・id は応答に含めない。</t>
+    r.getOvertimeMinutes(),
+    breaks);                               // List&lt;BreakItem&gt;（空リスト可）
+// toBreakItem: new BreakItem(b.getKind(), AppTime.toIso(b.getStartAt()), AppTime.toIso(b.getEndAt()))   // endAt が NULL なら null</t>
         </is>
       </c>
       <c r="C54" s="9" t="n"/>
@@ -4365,45 +4831,45 @@
       <c r="E54" s="9" t="n"/>
       <c r="F54" s="10" t="n"/>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>6.5  AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n"/>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>AppTime#toIso</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="10" t="n"/>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Entity を画面に直接返さない（KF-DD-002 層間IF）。user_id・id は応答に含めない。</t>
+        </is>
+      </c>
       <c r="C56" s="9" t="n"/>
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="10" t="n"/>
     </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Repository（Spring Data JPA・本処理で追加）</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="10" t="n"/>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>List&lt;AttendanceRecord&gt; findByUserIdAndWorkDateBetweenOrderByWorkDateAsc(Long userId, LocalDate from, LocalDate to)</t>
-        </is>
-      </c>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>6.5  AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n"/>
       <c r="C58" s="9" t="n"/>
       <c r="D58" s="9" t="n"/>
       <c r="E58" s="9" t="n"/>
@@ -4412,12 +4878,12 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>種別</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>ユーザーの勤務日が from〜to（両端を含む）の打刻行を、勤務日の昇順で返す。</t>
+          <t>Repository（Spring Data JPA・本処理で追加）</t>
         </is>
       </c>
       <c r="C59" s="9" t="n"/>
@@ -4428,12 +4894,12 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>interface AttendanceRecordRepository extends JpaRepository&lt;AttendanceRecord, Long&gt;</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>List&lt;AttendanceRecord&gt; findByUserIdAndWorkDateBetweenOrderByWorkDateAsc(Long userId, LocalDate from, LocalDate to)</t>
         </is>
       </c>
       <c r="C60" s="9" t="n"/>
@@ -4442,59 +4908,51 @@
       <c r="F60" s="10" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>ユーザーの勤務日が from〜to（両端を含む）の打刻行を、勤務日の昇順で返す。</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n"/>
       <c r="D61" s="9" t="n"/>
       <c r="E61" s="9" t="n"/>
       <c r="F61" s="10" t="n"/>
     </row>
     <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>userId</t>
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
+          <t>interface AttendanceRecordRepository extends JpaRepository&lt;AttendanceRecord, Long&gt;</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n"/>
       <c r="D62" s="9" t="n"/>
       <c r="E62" s="9" t="n"/>
       <c r="F62" s="10" t="n"/>
     </row>
     <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>LocalDate</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>期間開始日（含む）＝月初日</t>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="D63" s="9" t="n"/>
@@ -4504,17 +4962,17 @@
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>期間終了日（含む）＝月末日</t>
+          <t>ユーザーID</t>
         </is>
       </c>
       <c r="D64" s="9" t="n"/>
@@ -4522,47 +4980,54 @@
       <c r="F64" s="10" t="n"/>
     </row>
     <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>from</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>List&lt;AttendanceRecord&gt;（該当なしは空リスト。null は返らない）</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="n"/>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>期間開始日（含む）＝月初日</t>
+        </is>
+      </c>
       <c r="D65" s="9" t="n"/>
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="10" t="n"/>
     </row>
     <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>例外</t>
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>to</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="n"/>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>期間終了日（含む）＝月末日</t>
+        </is>
+      </c>
       <c r="D66" s="9" t="n"/>
       <c r="E66" s="9" t="n"/>
       <c r="F66" s="10" t="n"/>
     </row>
-    <row r="67" ht="34" customHeight="1">
+    <row r="67" ht="19" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>実装クラスは作らない。メソッド名から Spring Data JPA が次の SQL を生成する。
-SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ? ORDER BY work_date ASC</t>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>List&lt;AttendanceRecord&gt;（該当なしは空リスト。null は返らない）</t>
         </is>
       </c>
       <c r="C67" s="9" t="n"/>
@@ -4573,12 +5038,12 @@
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>（DB: attendance_records）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C68" s="9" t="n"/>
@@ -4589,13 +5054,13 @@
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Between は両端を含む（&gt;= from AND &lt;= to）。インデックス idx_att_user_date (user_id, work_date) が使われる。
-ロックは取らない（参照のみ）。</t>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>実装クラスは作らない。メソッド名から Spring Data JPA が次の SQL を生成する。
+SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ? ORDER BY work_date ASC</t>
         </is>
       </c>
       <c r="C69" s="9" t="n"/>
@@ -4603,46 +5068,46 @@
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="10" t="n"/>
     </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>6.6  MonthlyAttendanceResponse / AttendanceItem#（DTO 定義）</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="n"/>
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>（DB: attendance_records）</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="10" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Between は両端を含む（&gt;= from AND &lt;= to）。インデックス idx_att_user_date (user_id, work_date) が使われる。
+ロックは取らない（参照のみ）。</t>
+        </is>
+      </c>
       <c r="C71" s="9" t="n"/>
       <c r="D71" s="9" t="n"/>
       <c r="E71" s="9" t="n"/>
       <c r="F71" s="10" t="n"/>
     </row>
-    <row r="72" ht="19" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>DTO（record）</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="n"/>
-      <c r="D72" s="9" t="n"/>
-      <c r="E72" s="9" t="n"/>
-      <c r="F72" s="10" t="n"/>
-    </row>
-    <row r="73" ht="34" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>public record MonthlyAttendanceResponse(List&lt;AttendanceItem&gt; records, int totalWorkMinutes, int totalOvertimeMinutes) {}
-public record AttendanceItem(String workDate, String clockIn, String clockOut, Integer workMinutes, Integer overtimeMinutes) {}</t>
-        </is>
-      </c>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>6.6  AttendanceBreakRepository#findByAttendanceRecordIdInOrderByStartAtAsc</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n"/>
       <c r="C73" s="9" t="n"/>
       <c r="D73" s="9" t="n"/>
       <c r="E73" s="9" t="n"/>
@@ -4651,12 +5116,12 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>種別</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>応答 DTO。record のコンポーネント名がそのまま JSON キー（camelCase）になる。</t>
+          <t>Repository（ONL-024 で定義したリポジトリに本処理で追加）</t>
         </is>
       </c>
       <c r="C74" s="9" t="n"/>
@@ -4667,12 +5132,12 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>なし（Jackson が record を直接シリアライズ）</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>List&lt;AttendanceBreak&gt; findByAttendanceRecordIdInOrderByStartAtAsc(Collection&lt;Long&gt; attendanceRecordIds)</t>
         </is>
       </c>
       <c r="C75" s="9" t="n"/>
@@ -4683,12 +5148,12 @@
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>引数</t>
+          <t>説明</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>複数の打刻行に属する区間を、開始時刻の昇順でまとめて返す。</t>
         </is>
       </c>
       <c r="C76" s="9" t="n"/>
@@ -4699,12 +5164,12 @@
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>戻り値</t>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>なし（Spring Data JPA の導出クエリ）</t>
         </is>
       </c>
       <c r="C77" s="9" t="n"/>
@@ -4713,34 +5178,41 @@
       <c r="F77" s="10" t="n"/>
     </row>
     <row r="78" ht="19" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="n"/>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
       <c r="D78" s="9" t="n"/>
       <c r="E78" s="9" t="n"/>
       <c r="F78" s="10" t="n"/>
     </row>
-    <row r="79" ht="34" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>null の clockIn / clockOut / workMinutes / overtimeMinutes は JSON でも null として出力する（キーを省略しない）。
-records が 0 件のときは [] を出力する（null にしない）。</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="n"/>
+    <row r="79" ht="19" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>attendanceRecordIds</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Collection&lt;Long&gt;</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>月内の attendance_records.id の一覧（空にしない。呼出し側で 0 件ならスキップ）</t>
+        </is>
+      </c>
       <c r="D79" s="9" t="n"/>
       <c r="E79" s="9" t="n"/>
       <c r="F79" s="10" t="n"/>
@@ -4748,12 +5220,12 @@
     <row r="80" ht="19" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>List&lt;AttendanceBreak&gt;</t>
         </is>
       </c>
       <c r="C80" s="9" t="n"/>
@@ -4764,12 +5236,12 @@
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Jackson の既定では null も出力される。spring.jackson.default-property-inclusion を non_null にしないこと。</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C81" s="9" t="n"/>
@@ -4777,83 +5249,321 @@
       <c r="E81" s="9" t="n"/>
       <c r="F81" s="10" t="n"/>
     </row>
+    <row r="82" ht="19" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_breaks WHERE attendance_record_id IN (?, ...) ORDER BY start_at</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="10" t="n"/>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>（DB: attendance_breaks。idx_attendance_breaks_record を利用）</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="10" t="n"/>
+    </row>
+    <row r="84" ht="19" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>空の Collection を渡すと IN () の扱いが処理系に依存するため、呼出し側で打刻行が 0 件のときは呼ばない。最大 31 個の ID。</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>6.7  MonthlyAttendanceResponse / AttendanceItem / BreakItem#（DTO 定義）</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="10" t="n"/>
+    </row>
+    <row r="87" ht="19" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>DTO（record）</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="10" t="n"/>
+    </row>
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>public record MonthlyAttendanceResponse(List&lt;AttendanceItem&gt; records, int totalWorkMinutes, int totalOvertimeMinutes) {}
+public record AttendanceItem(String workDate, String clockIn, String clockOut, Integer workMinutes, Integer overtimeMinutes, List&lt;BreakItem&gt; breaks) {}
+public record BreakItem(String kind, String startAt, String endAt) {}</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="10" t="n"/>
+    </row>
+    <row r="89" ht="19" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>応答 DTO。record のコンポーネント名がそのまま JSON キー（camelCase）になる。</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="10" t="n"/>
+    </row>
+    <row r="90" ht="19" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>なし（Jackson が record を直接シリアライズ）</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="10" t="n"/>
+    </row>
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>引数</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="10" t="n"/>
+    </row>
+    <row r="92" ht="19" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="10" t="n"/>
+    </row>
+    <row r="93" ht="19" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="10" t="n"/>
+    </row>
+    <row r="94" ht="49" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>null の clockIn / clockOut / workMinutes / overtimeMinutes は JSON でも null として出力する（キーを省略しない）。
+records が 0 件のときは [] を出力する（null にしない）。
+breaks は区間がない日も [] を出力する（null にしない）。BreakItem.endAt が null の区間（継続中）は null で出力する。</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="10" t="n"/>
+    </row>
+    <row r="95" ht="19" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="10" t="n"/>
+    </row>
+    <row r="96" ht="19" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Jackson の既定では null も出力される。spring.jackson.default-property-inclusion を non_null にしないこと。</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="89">
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C51:F51"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B91:F91"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="B93:F93"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="C62:F62"/>
     <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B61:F61"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B57:F57"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="C64:F64"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B34:F34"/>
     <mergeCell ref="C35:F35"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="A30:F30"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="B65:F65"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B89:F89"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4866,7 +5576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F21"/>
+  <dimension ref="A2:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5121,7 +5831,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>勤務時間（分）。休憩控除後</t>
+          <t>勤務時間（分）。休憩・離席の控除後</t>
         </is>
       </c>
     </row>
@@ -5221,132 +5931,355 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>■ attendance_breaks</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>DB列</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Entityフィールド</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Java型</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>この処理での使用</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>attendance_record_id</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>attendanceRecordId</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>○ 検索条件（IN）・グループ化キー</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>FK attendance_records(id)。idx_attendance_breaks_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力（breaks[].kind）</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>BREAK / AWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>start_at</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>startAt</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力（breaks[].startAt）・並び順</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>TIMESTAMP（JST）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>end_at</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>endAt</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力（breaks[].endAt。NULL は null）</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>NULL = 継続中</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>id / created_at / updated_at</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>id / createdAt / updatedAt</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>— 応答に含めない</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>詳細は ONL-024 の 7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="79" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="79" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>月次の打刻記録の検索（AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc）</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ? ORDER BY work_date ASC
   -- 例: user_id = 3, work_date BETWEEN '2026-10-01' AND '2026-10-31'。最大31行</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="79" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>月内の区間の取得（AttendanceBreakRepository#findByAttendanceRecordIdInOrderByStartAtAsc）</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_breaks WHERE attendance_record_id IN (?, ?, ...) ORDER BY start_at
+  -- 打刻行が 0 件のときは実行しない。最大 31 個の ID</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>7.3 設定値</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>（Bean）Clock</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>config/ClockConfig.java</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Clock.system(Asia/Tokyo)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>ONL-002 で定義。「未来月」の判定に使用</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="49" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="49" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>spring.jackson.default-property-inclusion</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>指定しない（既定 ALWAYS）</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>null の項目も JSON に出力するため non_null にしない</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
